--- a/Results/Study 2/Confusion Matrices (validation images).xlsx
+++ b/Results/Study 2/Confusion Matrices (validation images).xlsx
@@ -410,21 +410,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>120</v>
-      </c>
-      <c r="C2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>119</v>
-      </c>
-      <c r="C3">
-        <v>41</v>
+        <v>90</v>
+      </c>
+      <c r="C2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>87</v>
+      </c>
+      <c r="C3">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -461,10 +461,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>123</v>
-      </c>
-      <c r="C3">
-        <v>37</v>
+        <v>114</v>
+      </c>
+      <c r="C3">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -490,21 +490,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>56</v>
-      </c>
-      <c r="C2">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>56</v>
-      </c>
-      <c r="C3">
-        <v>104</v>
+        <v>72</v>
+      </c>
+      <c r="C2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>72</v>
+      </c>
+      <c r="C3">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -530,21 +530,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>129</v>
-      </c>
-      <c r="C2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>124</v>
-      </c>
-      <c r="C3">
-        <v>36</v>
+        <v>121</v>
+      </c>
+      <c r="C2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>102</v>
+      </c>
+      <c r="C3">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -570,21 +570,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>145</v>
-      </c>
-      <c r="C2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>128</v>
-      </c>
-      <c r="C3">
-        <v>32</v>
+        <v>133</v>
+      </c>
+      <c r="C2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>112</v>
+      </c>
+      <c r="C3">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -610,21 +610,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>64</v>
-      </c>
-      <c r="C2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>66</v>
-      </c>
-      <c r="C3">
-        <v>94</v>
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>75</v>
+      </c>
+      <c r="C3">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -650,10 +650,90 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>96</v>
-      </c>
-      <c r="C2">
-        <v>64</v>
+        <v>92</v>
+      </c>
+      <c r="C2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>80</v>
+      </c>
+      <c r="C3">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>118</v>
+      </c>
+      <c r="C2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>115</v>
+      </c>
+      <c r="C3">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2">
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -672,86 +752,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>123</v>
-      </c>
-      <c r="C2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>122</v>
-      </c>
-      <c r="C3">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>101</v>
-      </c>
-      <c r="C2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>106</v>
-      </c>
-      <c r="C3">
-        <v>54</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C3"/>
@@ -770,21 +770,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>131</v>
-      </c>
-      <c r="C2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>126</v>
-      </c>
-      <c r="C3">
-        <v>34</v>
+        <v>146</v>
+      </c>
+      <c r="C2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>141</v>
+      </c>
+      <c r="C3">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -810,21 +810,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>94</v>
-      </c>
-      <c r="C2">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>93</v>
-      </c>
-      <c r="C3">
-        <v>67</v>
+        <v>92</v>
+      </c>
+      <c r="C2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>83</v>
+      </c>
+      <c r="C3">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -850,21 +850,21 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>64</v>
-      </c>
-      <c r="C2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>64</v>
-      </c>
-      <c r="C3">
-        <v>96</v>
+        <v>80</v>
+      </c>
+      <c r="C2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>80</v>
+      </c>
+      <c r="C3">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
